--- a/data/lookup/lqas_lookup.xlsx
+++ b/data/lookup/lqas_lookup.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R2906f8ccfcbb47dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R69feeb7360e645e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3303,6 +3303,70 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>BOTSWANA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BOT-2026-02-1_nOPV_NID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46147</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46150</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.987012987012987</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.435048387096774</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.474020458036587</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BOT-2026-02-1_nOPV_NIDRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>BURKINA FASO</x:t>
         </x:is>
       </x:c>
@@ -4670,10 +4734,10 @@
         <x:v>0.988977272727273</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.985424174174174</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.983391890891891</x:v>
+        <x:v>0.9859496996997</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.983567066067066</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0.97260273999999991</x:v>
@@ -4734,10 +4798,10 @@
         <x:v>0.993425925925926</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.992196969696969</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.991711128377795</x:v>
+        <x:v>0.992386363636362</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.991774259690926</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0</x:v>
@@ -6515,6 +6579,70 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>CHAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CHD-2026-03_nOPV_NID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46146</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.979166666666667</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975115283267457</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.973618867243868</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975966939059331</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.23566879</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CHD-2026-03_nOPV_NIDRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>CÔTE D’IVOIRE</x:t>
         </x:is>
       </x:c>
@@ -8766,10 +8894,10 @@
         <x:v>0.970847902097902</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.94096554834055</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96900191937692</x:v>
+        <x:v>0.941517364579866</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.969185858123359</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0.83236993999999986</x:v>
@@ -9075,13 +9203,13 @@
         <x:v>0.991071428571429</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.706779609279609</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.638678713418825</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.778843250423288</x:v>
+        <x:v>0.707912087912088</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.64701677794898</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.782000098144166</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0.07330827</x:v>
@@ -11014,6 +11142,60 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>ETH-2026-05-bOPV2-sNID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46149</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46152</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9">
+        <x:v>0.937277777777778</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.892121212121212</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ETH-2026-05-bOPV2-sNIDRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ETHIOPIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>ETH-ORO-3</x:t>
         </x:is>
       </x:c>
@@ -15679,12 +15861,12 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>In Progress</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>In Progress</x:t>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c s="9">
@@ -15694,10 +15876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.953551724137931</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.645787082649152</x:v>
+        <x:v>0.955051724137931</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.646287082649152</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0</x:v>
@@ -16564,16 +16746,16 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.987379807692308</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.911111111111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.844131944444444</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.914207621082621</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.965753968253968</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.962105902777779</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975953290343916</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0</x:v>
@@ -16805,12 +16987,12 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>In Progress</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>In Progress</x:t>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
         </x:is>
       </x:c>
       <x:c s="9">
@@ -19381,13 +19563,13 @@
         <x:v>0.94948107448107411</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.763925925925926</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.518576388888888</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.743994463098629</x:v>
+        <x:v>0.962092592592593</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.916087361712365</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.942553676262011</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0.04166667</x:v>
@@ -20260,46 +20442,3566 @@
         </x:is>
       </x:c>
       <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.434895833333333</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.571917808219178</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.33560454718417</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.26027397</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-2026-03_nOPV_NIDsRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIGER</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-72DS-02-2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44714</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44718</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.981423611111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.979775494672756</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.987066368594622</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.26027397</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>73</x:v>
+        <x:v>0.947916666666667</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.946566358024691</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96482767489711885</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-72DS-02-2022Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIGER</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-72DS-02-2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44741</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44744</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.972222222222222</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.911265432098766</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.90465893108298212</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.92938219513465692</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.69014084999999992</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-72DS-02-2022Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIGER</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-72DS-02-2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44862</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44865</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.9375</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.94642857142857084</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96130952380952406</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-72DS-02-2022Round 3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIGER</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-9DS-06-2021_Zinder</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44435</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44438</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.933333333333333</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.84</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.924444444444444</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-9DS-06-2021_ZinderRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIGER</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-9DS-06-2021_Zinder</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44456</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44459</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIG-9DS-06-2021_ZinderRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GUINEA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV - Guinea</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44491</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44493</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV - GuineaRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV- CAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44491</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44494</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV- CARRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CHAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV -CHAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44498</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44500</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV -CHADRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CHAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV -CHAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44519</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44522</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preventive campaign bOPV -CHADRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-04-01_nOPV_NIDs</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45771</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45774</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96334706959707</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.924206349206349</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.944842857142857</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.944132091982092</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.85714286000000006</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-04-01_nOPV_NIDsRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-04-01_nOPV_NIDs</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45834</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45838</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975206043956044</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.909484126984127</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.945198412698413</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.943296194546195</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.85714286000000006</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-04-01_nOPV_NIDsRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-10-01_nOPV_NIDs</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2, nOPV2 &amp; bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45989</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45994</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.9875</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.924404761904762</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.937728715728716</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.949877825877826</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.71428571000000007</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-10-01_nOPV_NIDsRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-10-01_nOPV_NIDs</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2, nOPV2 &amp; bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46122</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46125</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.979166666666667</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.939960317460318</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.989571428571429</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.969566137566138</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.97142856999999994</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RCA-2025-10-01_nOPV_NIDsRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RSS-2025-08-01_nOPV-sNID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45923</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45926</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.902081043956044</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.951444444444445</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.883945833333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.912490440577941</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RSS-2025-08-01_nOPV-sNIDRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RSS-2025-08-01_nOPV-sNID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45965</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45968</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.861528159340659</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.812611111111111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.739006944444444</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.804382071632071</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RSS-2025-08-01_nOPV-sNIDRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RWANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RWA-2023-07-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45131</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45135</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.991071428571429</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.989333333333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.959492753623188</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.979965838509317</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RWA-2023-07-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RWANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RWA-2023-07-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45180</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45184</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.981770833333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975333333333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.979333333333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978812500000001</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RWA-2023-07-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SENEGAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEN-79DS-01-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44547</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44550</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978214285714286</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.89164728682170613</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.95662052417866394</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEN-79DS-01-2021Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SENEGAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEN-79DS-01-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44616</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44619</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978214285714286</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.89164728682170613</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.95662052417866394</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEN-79DS-01-2021Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SENEGAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEN-79DS-01-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44783</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44785</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.87777777777777788</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.958333333333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.929166666666667</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.92175925925926</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SEN-79DS-01-2021Round 3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SIERRA LEONE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-16DS-01-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44344</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44347</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9">
+        <x:v>0.955555555555556</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.9765625</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-16DS-01-2021Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SIERRA LEONE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-16DS-01-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44379</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44382</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-16DS-01-2021Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SIERRA LEONE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-16DS-01-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44435</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44438</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-16DS-01-2021Round 3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SIERRA LEONE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-2024-05-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45422</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45425</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.983333333333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-2024-05-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SIERRA LEONE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-2024-05-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45450</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45453</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.984375</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.956</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.954652777777778</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96500925925925907</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-2024-05-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SIERRA LEONE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-2024-05-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45562</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45565</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.989583333333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.973</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.97375</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.97877777777777786</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SLE-2024-05-01_nOPVRound 3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-02-01_nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45349</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45352</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.933928571428571</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.910011111111111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.882948611111111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.908962764550264</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-02-01_nOPV2Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-02-01_nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45398</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45402</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.968154761904762</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.841416666666667</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.779423611111111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.862998346560847</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.3875</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-02-01_nOPV2Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-10-01_nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45607</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45612</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-10-01_nOPV2Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-10-01_nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45692</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45697</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.917829670329671</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.731322222222222</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.674547222222222</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.774566371591372</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.4375</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2024-10-01_nOPV2Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2026-01-05_nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV, nOPV2 &amp; bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46149</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46152</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.758138736263736</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.81125</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.767314814814815</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.77890118369285</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-2026-01-05_nOPV2Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-79DS-09-2020</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44145</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44176</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-79DS-09-2020Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SOUTH SUDAN</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-79DS-09-2020</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44243</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44245</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SSD-79DS-09-2020Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DEMOCRATIC REPUBLIC OF THE CONGO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Tanganyika</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44952</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44955</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.939339826839827</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.963113275613276</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TanganyikaRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2023-05-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45190</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45193</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.947569826007326</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.997222222222222</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.996801801801802</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.980531283343783</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2023-05-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2023-05-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45232</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45235</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.942022664835165</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975685185185185</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978154654654655</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.965287501558335</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.97297296999999994</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2023-05-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2026-02-01_nOPV_sNID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.91828231292517</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.990198412698413</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.984255555555556</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.964245427059713</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2026-02-01_nOPV_sNIDRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2026-02-01_nOPV_sNID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46149</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46152</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.994791666666667</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.994761904761905</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.994933333333333</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.994828968253968</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TNZ-2026-02-01_nOPV_sNIDRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOGO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-2025-11-01_nOPV_sNIDs</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46093</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46096</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-2025-11-01_nOPV_sNIDsRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOGO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-2025-11-01_nOPV_sNIDs</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46128</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.99375</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.99482905982906</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.99619301994302</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.64285714</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-2025-11-01_nOPV_sNIDsRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOGO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-39DS-06-022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44788</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44791</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978472222222222</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.973967236467237</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.98414648622982</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-39DS-06-022Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOGO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-39DS-06-022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44847</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44850</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.927083333333333</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.900641025641026</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.942574786324786</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TOG-39DS-06-022Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44644</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44647</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44699</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44702</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 3</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44805</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44808</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022Round 3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 4</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44896</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44899</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>TZA...DS-02-2022Round 4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-149DS-08-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44575</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44577</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.764685185185185</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>68.920563271605</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>23.5617494855967</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-149DS-08-2021Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-149DS-08-2021</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44862</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44864</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.633333333333333</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.984259259259259</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.539197530864197</x:v>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-149DS-08-2021Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-2024-08-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45567</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45571</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.992788461538462</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.699791666666666</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96294671201814</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.885175613407756</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-2024-08-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-2024-08-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45605</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.928685897435898</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.124513888888889</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.911959183673469</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.655052989999419</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.83333333</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGA-2024-08-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Uganda_2023</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44869</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44875</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Uganda_2023Round 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>UGANDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Uganda_2023</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44953</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44956</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="9"/>
+      <x:c s="10"/>
+      <x:c s="10"/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Uganda_2023Round 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAMBIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-02-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>44973</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>44976</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.993055555555556</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.996666666666667</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.996612403100775</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.995444875107666</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-02-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAMBIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-02-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45036</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45039</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.982312925170068</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.970861111111111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.991501147842057</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.981558394707745</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-02-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAMBIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-05-01_bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45096</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45101</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.997435897435898</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.977711111111111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.00110249042146</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.992083166322823</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96460176999999991</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-05-01_bOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAMBIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-09-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45169</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45173</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.996875</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>3.81128571428571</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.944497416020672</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.91755271010213</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.98765432</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-09-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAMBIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-09-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45225</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45228</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.995625</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.977539682539683</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.961915923945336</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978360202161673</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96341463</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2023-09-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAMBIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2024-06-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45498</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45501</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.985918367346939</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.99125</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96381975308642</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.980329373477786</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.95555556</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2024-06-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAMBIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZAM-2026-03-01_nOPV-sNID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 1</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>46132</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.989027777777778</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.946571321321321</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978533033033033</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.26760563</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>71</x:v>
       </x:c>
       <x:c s="10">
         <x:v>19</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>NIG-2026-03_nOPV_NIDsRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-72DS-02-2022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
+          <x:t>ZAM-2026-03-01_nOPV-sNIDRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIMBABWE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-05-01_bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -20308,62 +24010,62 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>44714</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44718</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.947916666666667</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.946566358024691</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96482767489711885</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-72DS-02-2022Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-72DS-02-2022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
+        <x:v>45069</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45072</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.822505411255411</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.932633405483406</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.909952380952381</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.888363732563733</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.59677419000000009</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-05-01_bOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIMBABWE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-05-01_bOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>bOPV</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -20372,121 +24074,57 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>44741</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44744</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.972222222222222</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.911265432098766</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.90465893108298212</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.92938219513465692</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.69014084999999992</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-72DS-02-2022Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-72DS-02-2022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44862</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44865</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9375</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.94642857142857084</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96130952380952406</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-72DS-02-2022Round 3</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-9DS-06-2021_Zinder</x:t>
+        <x:v>45209</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45213</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.994047619047619</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.966853174603175</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.957283068783069</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.972727954144621</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.91935484</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-05-01_bOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIMBABWE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-12-01_nOPV</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -20500,57 +24138,57 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>44435</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44438</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.933333333333333</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.84</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.924444444444444</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-9DS-06-2021_ZinderRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-9DS-06-2021_Zinder</x:t>
+        <x:v>45342</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45345</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.953571428571428</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.970783333333333</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.951382716049383</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.958579159318048</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96774193999999991</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-12-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIMBABWE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-12-01_nOPV</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -20564,48 +24202,62 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>44456</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44459</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIG-9DS-06-2021_ZinderRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>GUINEA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV - Guinea</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t/>
+        <x:v>45370</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45373</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.891751700680272</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.963105555555556</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.944925925925926</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.933261060720584</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.85483871</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2023-12-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIMBABWE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2024-11-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -20614,48 +24266,126 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>44491</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44493</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV - GuineaRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV- CAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
+        <x:v>45622</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45625</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.986355311355312</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.975711111111111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.948994708994708</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.970353710487044</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.93548387</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2024-11-01_nOPVRound 1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIMBABWE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2024-11-01_nOPV</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Round 2</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>45692</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>45697</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Finished</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.978346415489273</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.963083333333334</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.964412698412698</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.968614149078435</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.95161289999999987</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2024-11-01_nOPVRound 2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIMBABWE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ZIM-2026-03-01_nOPV_sNID</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>nOPV2</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -20664,2990 +24394,6 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>44491</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44494</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV- CARRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CHAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV -CHAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44498</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44500</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV -CHADRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CHAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV -CHAD</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44519</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44522</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Preventive campaign bOPV -CHADRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-04-01_nOPV_NIDs</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45771</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45774</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96334706959707</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.924206349206349</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.944842857142857</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.944132091982092</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.85714286000000006</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-04-01_nOPV_NIDsRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-04-01_nOPV_NIDs</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45834</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45838</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.975206043956044</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.909484126984127</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.945198412698413</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.943296194546195</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.85714286000000006</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-04-01_nOPV_NIDsRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-10-01_nOPV_NIDs</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2, nOPV2 &amp; bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45989</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45994</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9875</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.924404761904762</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.937728715728716</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.949877825877826</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.71428571000000007</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-10-01_nOPV_NIDsRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRAL AFRICAN REPUBLIC</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-10-01_nOPV_NIDs</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2, nOPV2 &amp; bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46122</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46125</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.979166666666667</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.939960317460318</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.989</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.969375661375662</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.97142856999999994</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RCA-2025-10-01_nOPV_NIDsRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RSS-2025-08-01_nOPV-sNID</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45923</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45926</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.902081043956044</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.951444444444445</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.883945833333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.912490440577941</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RSS-2025-08-01_nOPV-sNIDRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RSS-2025-08-01_nOPV-sNID</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45965</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45968</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.861528159340659</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.812611111111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.739006944444444</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.804382071632071</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RSS-2025-08-01_nOPV-sNIDRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RWANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RWA-2023-07-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45131</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45135</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.991071428571429</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.989333333333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.959492753623188</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.979965838509317</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RWA-2023-07-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RWANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RWA-2023-07-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45180</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45184</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.981770833333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.975333333333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.979333333333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.978812500000001</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RWA-2023-07-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SENEGAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SEN-79DS-01-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44547</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44550</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.978214285714286</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.89164728682170613</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.95662052417866394</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SEN-79DS-01-2021Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SENEGAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SEN-79DS-01-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44616</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44619</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.978214285714286</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.89164728682170613</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.95662052417866394</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SEN-79DS-01-2021Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SENEGAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SEN-79DS-01-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44783</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44785</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.87777777777777788</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.958333333333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.929166666666667</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.92175925925926</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SEN-79DS-01-2021Round 3</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SIERRA LEONE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-16DS-01-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44344</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44347</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9">
-        <x:v>0.955555555555556</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9765625</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-16DS-01-2021Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SIERRA LEONE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-16DS-01-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44379</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44382</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-16DS-01-2021Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SIERRA LEONE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-16DS-01-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44435</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44438</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-16DS-01-2021Round 3</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SIERRA LEONE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-2024-05-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45422</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45425</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.975</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.975</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.983333333333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-2024-05-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SIERRA LEONE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-2024-05-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45450</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45453</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.984375</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.956</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.954652777777778</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96500925925925907</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-2024-05-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SIERRA LEONE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-2024-05-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45562</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45565</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.989583333333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.973</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.97375</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.97877777777777786</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SLE-2024-05-01_nOPVRound 3</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-02-01_nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45349</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45352</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.933928571428571</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.910011111111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.882948611111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.908962764550264</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-02-01_nOPV2Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-02-01_nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45398</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45402</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.968154761904762</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.841416666666667</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.779423611111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.862998346560847</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.3875</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-02-01_nOPV2Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-10-01_nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45607</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45612</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-10-01_nOPV2Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-10-01_nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45692</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45697</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.917829670329671</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.731322222222222</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.674547222222222</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.774566371591372</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.4375</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-2024-10-01_nOPV2Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-79DS-09-2020</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44145</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44176</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-79DS-09-2020Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SOUTH SUDAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-79DS-09-2020</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44243</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44245</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SSD-79DS-09-2020Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>DEMOCRATIC REPUBLIC OF THE CONGO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Tanganyika</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44952</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44955</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.939339826839827</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.963113275613276</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TanganyikaRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TNZ-2023-05-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45190</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45193</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.947569826007326</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.997222222222222</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.996801801801802</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.980531283343783</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TNZ-2023-05-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TNZ-2023-05-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45232</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45235</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.942022664835165</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.975685185185185</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.978154654654655</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.965287501558335</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.97297296999999994</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TNZ-2023-05-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TNZ-2026-02-01_nOPV_sNID</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.974458874458874</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.993571428571429</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.987966666666667</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.985332323232323</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TNZ-2026-02-01_nOPV_sNIDRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOGO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-2025-11-01_nOPV_sNIDs</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46093</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46096</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-2025-11-01_nOPV_sNIDsRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOGO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-2025-11-01_nOPV_sNIDs</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46128</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.99375</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.99482905982906</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.99619301994302</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.64285714</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-2025-11-01_nOPV_sNIDsRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOGO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-39DS-06-022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44788</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44791</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.978472222222222</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.973967236467237</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.98414648622982</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-39DS-06-022Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOGO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-39DS-06-022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44847</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44850</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.927083333333333</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.900641025641026</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.942574786324786</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TOG-39DS-06-022Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44644</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44647</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44699</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44702</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44805</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44808</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022Round 3</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UNITED REPUBLIC OF TANZANIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 4</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44896</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44899</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>TZA...DS-02-2022Round 4</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-149DS-08-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44575</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44577</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.764685185185185</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>68.920563271605</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>23.5617494855967</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-149DS-08-2021Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-149DS-08-2021</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44862</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44864</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.633333333333333</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.984259259259259</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.539197530864197</x:v>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-149DS-08-2021Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-2024-08-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45567</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45571</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.992788461538462</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.699791666666666</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96294671201814</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.885175613407756</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-2024-08-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-2024-08-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45605</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45609</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.928685897435898</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.124513888888889</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.911959183673469</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.655052989999419</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.83333333</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGA-2024-08-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Uganda_2023</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44869</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44875</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Uganda_2023Round 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>UGANDA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Uganda_2023</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44953</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44956</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="9"/>
-      <x:c s="10"/>
-      <x:c s="10"/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Uganda_2023Round 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAMBIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-02-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>44973</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>44976</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.993055555555556</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.996666666666667</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.996612403100775</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.995444875107666</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-02-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAMBIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-02-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45036</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45039</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.982312925170068</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.970861111111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.991501147842057</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.981558394707745</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-02-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAMBIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-05-01_bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45096</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45101</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.997435897435898</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.977711111111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.00110249042146</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.992083166322823</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96460176999999991</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-05-01_bOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAMBIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-09-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45169</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45173</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.996875</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>3.81128571428571</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.944497416020672</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.91755271010213</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.98765432</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-09-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAMBIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-09-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45225</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45228</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.995625</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.977539682539683</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.961915923945336</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.978360202161673</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96341463</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2023-09-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAMBIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2024-06-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45498</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45501</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.985918367346939</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.99125</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96381975308642</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.980329373477786</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.95555556</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2024-06-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAMBIA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2026-03-01_nOPV-sNID</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
         <x:v>46132</x:v>
       </x:c>
       <x:c s="8">
@@ -23664,455 +24410,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.987138888888889</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.945895645645646</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.977678178178178</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.26760563</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZAM-2026-03-01_nOPV-sNIDRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIMBABWE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-05-01_bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45069</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45072</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.822505411255411</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.932633405483406</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.909952380952381</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.888363732563733</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.59677419000000009</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-05-01_bOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIMBABWE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-05-01_bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>bOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45209</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45213</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.994047619047619</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.966853174603175</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.957283068783069</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.972727954144621</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.91935484</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-05-01_bOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIMBABWE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-12-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45342</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45345</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.953571428571428</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.970783333333333</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.951382716049383</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.958579159318048</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96774193999999991</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-12-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIMBABWE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-12-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45370</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45373</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.891751700680272</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.963105555555556</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.944925925925926</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.933261060720584</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.85483871</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2023-12-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIMBABWE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2024-11-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45622</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45625</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.986355311355312</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.975711111111111</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.948994708994708</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.970353710487044</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.93548387</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2024-11-01_nOPVRound 1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIMBABWE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2024-11-01_nOPV</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>45692</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>45697</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.978346415489273</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.963083333333334</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.964412698412698</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.968614149078435</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.95161289999999987</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2024-11-01_nOPVRound 2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIMBABWE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ZIM-2026-03-01_nOPV_sNID</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>nOPV2</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Round 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>46132</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Finished</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.907326007326008</x:v>
+        <x:v>0.92518315018315</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0.945222222222222</x:v>
@@ -24121,7 +24419,7 @@
         <x:v>0.520191873098653</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.790913367548961</x:v>
+        <x:v>0.796865748501342</x:v>
       </x:c>
       <x:c s="9">
         <x:v>0</x:v>

--- a/data/lookup/lqas_lookup.xlsx
+++ b/data/lookup/lqas_lookup.xlsx
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>bOPV, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>bOPV, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>bOPV, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>bOPV, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>nOPV2, nOPV2 &amp; bOPV</t>
+          <t>nOPV2 &amp; bOPV</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
